--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441190</v>
+        <v>113441301</v>
       </c>
       <c r="B2" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788306</v>
+        <v>788273</v>
       </c>
       <c r="R2" t="n">
-        <v>7217284</v>
+        <v>7217330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441179</v>
+        <v>113441307</v>
       </c>
       <c r="B3" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788273</v>
+        <v>788306</v>
       </c>
       <c r="R3" t="n">
-        <v>7217330</v>
+        <v>7217284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441349</v>
+        <v>113441230</v>
       </c>
       <c r="B4" t="n">
-        <v>90310</v>
+        <v>90326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441176</v>
+        <v>113441299</v>
       </c>
       <c r="B5" t="n">
-        <v>89993</v>
+        <v>90009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441301</v>
+        <v>113441190</v>
       </c>
       <c r="B2" t="n">
         <v>90045</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788273</v>
+        <v>788306</v>
       </c>
       <c r="R2" t="n">
-        <v>7217330</v>
+        <v>7217284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441307</v>
+        <v>113441176</v>
       </c>
       <c r="B3" t="n">
-        <v>90045</v>
+        <v>90009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788306</v>
+        <v>788389</v>
       </c>
       <c r="R3" t="n">
-        <v>7217284</v>
+        <v>7217274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441230</v>
+        <v>113441179</v>
       </c>
       <c r="B4" t="n">
-        <v>90326</v>
+        <v>90045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788274</v>
+        <v>788273</v>
       </c>
       <c r="R4" t="n">
-        <v>7217336</v>
+        <v>7217330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441299</v>
+        <v>113441230</v>
       </c>
       <c r="B5" t="n">
-        <v>90009</v>
+        <v>90326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788389</v>
+        <v>788274</v>
       </c>
       <c r="R5" t="n">
-        <v>7217274</v>
+        <v>7217336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441190</v>
+        <v>113441307</v>
       </c>
       <c r="B2" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441176</v>
+        <v>113441301</v>
       </c>
       <c r="B3" t="n">
-        <v>90009</v>
+        <v>90057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788389</v>
+        <v>788273</v>
       </c>
       <c r="R3" t="n">
-        <v>7217274</v>
+        <v>7217330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441179</v>
+        <v>113441299</v>
       </c>
       <c r="B4" t="n">
-        <v>90045</v>
+        <v>90021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788273</v>
+        <v>788389</v>
       </c>
       <c r="R4" t="n">
-        <v>7217330</v>
+        <v>7217274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>113441230</v>
       </c>
       <c r="B5" t="n">
-        <v>90326</v>
+        <v>90338</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441307</v>
+        <v>113441299</v>
       </c>
       <c r="B2" t="n">
-        <v>90057</v>
+        <v>90021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788306</v>
+        <v>788389</v>
       </c>
       <c r="R2" t="n">
-        <v>7217284</v>
+        <v>7217274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441301</v>
+        <v>113441349</v>
       </c>
       <c r="B3" t="n">
-        <v>90057</v>
+        <v>90338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788273</v>
+        <v>788274</v>
       </c>
       <c r="R3" t="n">
-        <v>7217330</v>
+        <v>7217336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441299</v>
+        <v>113441308</v>
       </c>
       <c r="B4" t="n">
-        <v>90021</v>
+        <v>90057</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788389</v>
+        <v>788306</v>
       </c>
       <c r="R4" t="n">
-        <v>7217274</v>
+        <v>7217284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441230</v>
+        <v>113441301</v>
       </c>
       <c r="B5" t="n">
-        <v>90338</v>
+        <v>90057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788274</v>
+        <v>788273</v>
       </c>
       <c r="R5" t="n">
-        <v>7217336</v>
+        <v>7217330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113441299</v>
       </c>
       <c r="B2" t="n">
-        <v>90021</v>
+        <v>90043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441349</v>
+        <v>113441188</v>
       </c>
       <c r="B3" t="n">
-        <v>90338</v>
+        <v>90079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788274</v>
+        <v>788306</v>
       </c>
       <c r="R3" t="n">
-        <v>7217336</v>
+        <v>7217284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441308</v>
+        <v>113441301</v>
       </c>
       <c r="B4" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788306</v>
+        <v>788273</v>
       </c>
       <c r="R4" t="n">
-        <v>7217284</v>
+        <v>7217330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441301</v>
+        <v>113441230</v>
       </c>
       <c r="B5" t="n">
-        <v>90057</v>
+        <v>90360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788273</v>
+        <v>788274</v>
       </c>
       <c r="R5" t="n">
-        <v>7217330</v>
+        <v>7217336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441299</v>
+        <v>113441301</v>
       </c>
       <c r="B2" t="n">
-        <v>90043</v>
+        <v>90083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788389</v>
+        <v>788273</v>
       </c>
       <c r="R2" t="n">
-        <v>7217274</v>
+        <v>7217330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441188</v>
+        <v>113441230</v>
       </c>
       <c r="B3" t="n">
-        <v>90079</v>
+        <v>90364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788306</v>
+        <v>788274</v>
       </c>
       <c r="R3" t="n">
-        <v>7217284</v>
+        <v>7217336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441301</v>
+        <v>113441308</v>
       </c>
       <c r="B4" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788273</v>
+        <v>788306</v>
       </c>
       <c r="R4" t="n">
-        <v>7217330</v>
+        <v>7217284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441230</v>
+        <v>113441176</v>
       </c>
       <c r="B5" t="n">
-        <v>90360</v>
+        <v>90047</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788274</v>
+        <v>788389</v>
       </c>
       <c r="R5" t="n">
-        <v>7217336</v>
+        <v>7217274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113441301</v>
       </c>
       <c r="B2" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441230</v>
+        <v>113441190</v>
       </c>
       <c r="B3" t="n">
-        <v>90364</v>
+        <v>90089</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788274</v>
+        <v>788306</v>
       </c>
       <c r="R3" t="n">
-        <v>7217336</v>
+        <v>7217284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441308</v>
+        <v>113441176</v>
       </c>
       <c r="B4" t="n">
-        <v>90083</v>
+        <v>90053</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788306</v>
+        <v>788389</v>
       </c>
       <c r="R4" t="n">
-        <v>7217284</v>
+        <v>7217274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441176</v>
+        <v>113441230</v>
       </c>
       <c r="B5" t="n">
-        <v>90047</v>
+        <v>90370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788389</v>
+        <v>788274</v>
       </c>
       <c r="R5" t="n">
-        <v>7217274</v>
+        <v>7217336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441190</v>
+        <v>113441176</v>
       </c>
       <c r="B3" t="n">
-        <v>90089</v>
+        <v>90053</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788306</v>
+        <v>788389</v>
       </c>
       <c r="R3" t="n">
-        <v>7217284</v>
+        <v>7217274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441176</v>
+        <v>113441190</v>
       </c>
       <c r="B4" t="n">
-        <v>90053</v>
+        <v>90089</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788389</v>
+        <v>788306</v>
       </c>
       <c r="R4" t="n">
-        <v>7217274</v>
+        <v>7217284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441230</v>
+        <v>113441349</v>
       </c>
       <c r="B5" t="n">
         <v>90370</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441301</v>
+        <v>113441179</v>
       </c>
       <c r="B2" t="n">
-        <v>90089</v>
+        <v>90096</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441176</v>
+        <v>113441299</v>
       </c>
       <c r="B3" t="n">
-        <v>90053</v>
+        <v>90060</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441190</v>
+        <v>113441230</v>
       </c>
       <c r="B4" t="n">
-        <v>90089</v>
+        <v>90377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788306</v>
+        <v>788274</v>
       </c>
       <c r="R4" t="n">
-        <v>7217284</v>
+        <v>7217336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441349</v>
+        <v>113441188</v>
       </c>
       <c r="B5" t="n">
-        <v>90370</v>
+        <v>90096</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788274</v>
+        <v>788306</v>
       </c>
       <c r="R5" t="n">
-        <v>7217336</v>
+        <v>7217284</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441179</v>
+        <v>113441190</v>
       </c>
       <c r="B2" t="n">
-        <v>90096</v>
+        <v>90099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788273</v>
+        <v>788306</v>
       </c>
       <c r="R2" t="n">
-        <v>7217330</v>
+        <v>7217284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441299</v>
+        <v>113441230</v>
       </c>
       <c r="B3" t="n">
-        <v>90060</v>
+        <v>90380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788389</v>
+        <v>788274</v>
       </c>
       <c r="R3" t="n">
-        <v>7217274</v>
+        <v>7217336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441230</v>
+        <v>113441179</v>
       </c>
       <c r="B4" t="n">
-        <v>90377</v>
+        <v>90099</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788274</v>
+        <v>788273</v>
       </c>
       <c r="R4" t="n">
-        <v>7217336</v>
+        <v>7217330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441188</v>
+        <v>113441299</v>
       </c>
       <c r="B5" t="n">
-        <v>90096</v>
+        <v>90063</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788306</v>
+        <v>788389</v>
       </c>
       <c r="R5" t="n">
-        <v>7217284</v>
+        <v>7217274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441190</v>
+        <v>113441349</v>
       </c>
       <c r="B2" t="n">
-        <v>90099</v>
+        <v>90411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788306</v>
+        <v>788274</v>
       </c>
       <c r="R2" t="n">
-        <v>7217284</v>
+        <v>7217336</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441230</v>
+        <v>113441179</v>
       </c>
       <c r="B3" t="n">
-        <v>90380</v>
+        <v>90130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788274</v>
+        <v>788273</v>
       </c>
       <c r="R3" t="n">
-        <v>7217336</v>
+        <v>7217330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441179</v>
+        <v>113441190</v>
       </c>
       <c r="B4" t="n">
-        <v>90099</v>
+        <v>90130</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788273</v>
+        <v>788306</v>
       </c>
       <c r="R4" t="n">
-        <v>7217330</v>
+        <v>7217284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441299</v>
+        <v>113441176</v>
       </c>
       <c r="B5" t="n">
-        <v>90063</v>
+        <v>90094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441349</v>
+        <v>113441188</v>
       </c>
       <c r="B2" t="n">
-        <v>90411</v>
+        <v>90131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788274</v>
+        <v>788306</v>
       </c>
       <c r="R2" t="n">
-        <v>7217336</v>
+        <v>7217284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441179</v>
+        <v>113441349</v>
       </c>
       <c r="B3" t="n">
-        <v>90130</v>
+        <v>90412</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788273</v>
+        <v>788274</v>
       </c>
       <c r="R3" t="n">
-        <v>7217330</v>
+        <v>7217336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441190</v>
+        <v>113441179</v>
       </c>
       <c r="B4" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788306</v>
+        <v>788273</v>
       </c>
       <c r="R4" t="n">
-        <v>7217284</v>
+        <v>7217330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>113441176</v>
       </c>
       <c r="B5" t="n">
-        <v>90094</v>
+        <v>90095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441188</v>
+        <v>113441176</v>
       </c>
       <c r="B2" t="n">
-        <v>90131</v>
+        <v>90099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788306</v>
+        <v>788389</v>
       </c>
       <c r="R2" t="n">
-        <v>7217284</v>
+        <v>7217274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441349</v>
+        <v>113441301</v>
       </c>
       <c r="B3" t="n">
-        <v>90412</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788274</v>
+        <v>788273</v>
       </c>
       <c r="R3" t="n">
-        <v>7217336</v>
+        <v>7217330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441179</v>
+        <v>113441230</v>
       </c>
       <c r="B4" t="n">
-        <v>90131</v>
+        <v>90416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788273</v>
+        <v>788274</v>
       </c>
       <c r="R4" t="n">
-        <v>7217330</v>
+        <v>7217336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441176</v>
+        <v>113441308</v>
       </c>
       <c r="B5" t="n">
-        <v>90095</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788389</v>
+        <v>788306</v>
       </c>
       <c r="R5" t="n">
-        <v>7217274</v>
+        <v>7217284</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41506-2021 artfynd.xlsx
+++ b/artfynd/A 41506-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
